--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.11945550147699</v>
+        <v>10.58191151899001</v>
       </c>
       <c r="D2" t="n">
-        <v>65.59876767090645</v>
+        <v>10.6597997465223</v>
       </c>
       <c r="E2" t="n">
-        <v>16.54128680848367</v>
+        <v>2.687959106378597</v>
       </c>
       <c r="F2" t="n">
-        <v>16.92461036321737</v>
+        <v>2.750249184022822</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.09274645324977</v>
+        <v>6.190071298653088</v>
       </c>
       <c r="D3" t="n">
-        <v>36.0526351325392</v>
+        <v>5.858553209037621</v>
       </c>
       <c r="E3" t="n">
-        <v>16.54128680848367</v>
+        <v>2.687959106378597</v>
       </c>
       <c r="F3" t="n">
-        <v>16.92461036321737</v>
+        <v>2.750249184022822</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.11077471159689</v>
+        <v>5.543000890634494</v>
       </c>
       <c r="D4" t="n">
-        <v>34.29175864293283</v>
+        <v>5.572410779476584</v>
       </c>
       <c r="E4" t="n">
-        <v>16.54128680848367</v>
+        <v>2.687959106378597</v>
       </c>
       <c r="F4" t="n">
-        <v>16.92461036321737</v>
+        <v>2.750249184022822</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.31233901618362</v>
+        <v>3.138255090129839</v>
       </c>
       <c r="D5" t="n">
-        <v>18.80563988725114</v>
+        <v>3.05591648167831</v>
       </c>
       <c r="E5" t="n">
-        <v>16.54128680848367</v>
+        <v>2.687959106378597</v>
       </c>
       <c r="F5" t="n">
-        <v>16.92461036321737</v>
+        <v>2.750249184022822</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
